--- a/branches/release/v2027.0.0-ballot.rc2/observations-summary.xlsx
+++ b/branches/release/v2027.0.0-ballot.rc2/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1430" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1430" uniqueCount="128">
   <si>
     <t>Profile</t>
   </si>
@@ -107,66 +107,69 @@
     <t>mii-pr-lungenfunktion-diffusionskapazitaet</t>
   </si>
   <si>
+    <t>MII PR Lungenfunktion Diffusionskapzität</t>
+  </si>
+  <si>
+    <t>mii-pr-lungenfunktion-dlco</t>
+  </si>
+  <si>
+    <t>MII PR Lungenfunktion DLCO</t>
+  </si>
+  <si>
+    <t>null#1366665001</t>
+  </si>
+  <si>
+    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-lungenfunktion/ValueSet/mii-vs-lufu-lnc-dlco (required)</t>
+  </si>
+  <si>
+    <t>SNOMED CT#TODO</t>
+  </si>
+  <si>
+    <t>mii-pr-lungenfunktion-dlcoc</t>
+  </si>
+  <si>
+    <t>MII PR Lungenfunktion DLCOc</t>
+  </si>
+  <si>
+    <t>null#TODO</t>
+  </si>
+  <si>
+    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-lungenfunktion/ValueSet/mii-vs-lufu-lnc-dlcoc (required)</t>
+  </si>
+  <si>
+    <t>SNOMED CT#TODO, LOINC#TODO</t>
+  </si>
+  <si>
+    <t>mii-pr-lungenfunktion-dosis</t>
+  </si>
+  <si>
+    <t>MII PR Lungenfunktion Dosis</t>
+  </si>
+  <si>
+    <t>mii-pr-lungenfunktion-fev</t>
+  </si>
+  <si>
+    <t>MII PR Lungenfunktion FEV</t>
+  </si>
+  <si>
+    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-lungenfunktion/ValueSet/mii-vs-lufu-lnc-fev (required)</t>
+  </si>
+  <si>
+    <t>mii-pr-lungenfunktion-fev-fvc</t>
+  </si>
+  <si>
+    <t>MII PR Lungenfunktion FEV/FVC</t>
+  </si>
+  <si>
+    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-lungenfunktion/ValueSet/mii-vs-lufu-lnc-fev-fvc (required)</t>
+  </si>
+  <si>
+    <t>mii-pr-lungenfunktion-fluss</t>
+  </si>
+  <si>
     <t>MII PR Lungenfunktion Fluss</t>
   </si>
   <si>
-    <t>mii-pr-lungenfunktion-dlco</t>
-  </si>
-  <si>
-    <t>MII PR Lungenfunktion DLCO</t>
-  </si>
-  <si>
-    <t>null#1366665001</t>
-  </si>
-  <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-lungenfunktion/ValueSet/mii-vs-lufu-lnc-dlco (required)</t>
-  </si>
-  <si>
-    <t>SNOMED CT#TODO</t>
-  </si>
-  <si>
-    <t>mii-pr-lungenfunktion-dlcoc</t>
-  </si>
-  <si>
-    <t>MII PR Lungenfunktion DLCOc</t>
-  </si>
-  <si>
-    <t>null#TODO</t>
-  </si>
-  <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-lungenfunktion/ValueSet/mii-vs-lufu-lnc-dlcoc (required)</t>
-  </si>
-  <si>
-    <t>SNOMED CT#TODO, LOINC#TODO</t>
-  </si>
-  <si>
-    <t>mii-pr-lungenfunktion-dosis</t>
-  </si>
-  <si>
-    <t>MII PR Lungenfunktion Dosis</t>
-  </si>
-  <si>
-    <t>mii-pr-lungenfunktion-fev</t>
-  </si>
-  <si>
-    <t>MII PR Lungenfunktion FEV</t>
-  </si>
-  <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-lungenfunktion/ValueSet/mii-vs-lufu-lnc-fev (required)</t>
-  </si>
-  <si>
-    <t>mii-pr-lungenfunktion-fev-fvc</t>
-  </si>
-  <si>
-    <t>MII PR Lungenfunktion FEV/FVC</t>
-  </si>
-  <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-lungenfunktion/ValueSet/mii-vs-lufu-lnc-fev-fvc (required)</t>
-  </si>
-  <si>
-    <t>mii-pr-lungenfunktion-fluss</t>
-  </si>
-  <si>
     <t>mii-pr-lungenfunktion-frc</t>
   </si>
   <si>
@@ -209,6 +212,15 @@
     <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-lungenfunktion/ValueSet/mii-vs-lufu-lnc-ic (required)</t>
   </si>
   <si>
+    <t>mii-pr-lungenfunktion-irv-erv</t>
+  </si>
+  <si>
+    <t>MII PR Lungenfunktion Reserve Volumen</t>
+  </si>
+  <si>
+    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-lungenfunktion/ValueSet/mii-vs-lufu-lnc-irv-erv (required)</t>
+  </si>
+  <si>
     <t>mii-pr-lungenfunktion-kco</t>
   </si>
   <si>
@@ -299,28 +311,19 @@
     <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-lungenfunktion/ValueSet/mii-vs-lufu-lnc-sr (required)</t>
   </si>
   <si>
-    <t>mii-pr-lungenfunktion-irv</t>
+    <t>mii-pr-lungenfunktion-rv</t>
   </si>
   <si>
     <t>MII PR Lungenfunktion RV</t>
   </si>
   <si>
+    <t>null#42457008</t>
+  </si>
+  <si>
     <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-lungenfunktion/ValueSet/mii-vs-lufu-lnc-rv (required)</t>
   </si>
   <si>
-    <t>mii-pr-lungenfunktion-rvl</t>
-  </si>
-  <si>
-    <t>MII PR Lungenfunktion RVL</t>
-  </si>
-  <si>
-    <t>null#42457008</t>
-  </si>
-  <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-lungenfunktion/ValueSet/mii-vs-lufu-lnc-rvl (required)</t>
-  </si>
-  <si>
-    <t>mii-pr-lungenfunktion-rvl-tlc</t>
+    <t>mii-pr-lungenfunktion-rv-tlc</t>
   </si>
   <si>
     <t>MII PR Lungenfunktion Anteil Residualvolumen an Lungenkapazität</t>
@@ -329,7 +332,7 @@
     <t>null#1366666000</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-lungenfunktion/ValueSet/mii-vs-lufu-lnc-rvl-tlc (required)</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-lungenfunktion/ValueSet/mii-vs-lufu-lnc-rv-tlc (required)</t>
   </si>
   <si>
     <t>mii-pr-lungenfunktion-sg-total</t>
@@ -378,6 +381,9 @@
   </si>
   <si>
     <t>mii-pr-lungenfunktion-viskositaet</t>
+  </si>
+  <si>
+    <t>MII PR Lungenfunktion Viskosität</t>
   </si>
   <si>
     <t>mii-pr-lungenfunktion-volumen</t>
@@ -1581,7 +1587,7 @@
         <v>50</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="C31" t="s" s="2">
         <v>13</v>
@@ -1616,7 +1622,7 @@
         <v>14</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="C32" t="s" s="2">
         <v>14</v>
@@ -1651,7 +1657,7 @@
         <v>14</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="C33" t="s" s="2">
         <v>14</v>
@@ -1686,7 +1692,7 @@
         <v>14</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="C34" t="s" s="2">
         <v>14</v>
@@ -1718,10 +1724,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C35" t="s" s="2">
         <v>13</v>
@@ -1730,10 +1736,10 @@
         <v>14</v>
       </c>
       <c r="E35" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F35" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>16</v>
@@ -1756,7 +1762,7 @@
         <v>14</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C36" t="s" s="2">
         <v>14</v>
@@ -1791,7 +1797,7 @@
         <v>14</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C37" t="s" s="2">
         <v>14</v>
@@ -1826,7 +1832,7 @@
         <v>14</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C38" t="s" s="2">
         <v>14</v>
@@ -1858,10 +1864,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C39" t="s" s="2">
         <v>13</v>
@@ -1873,7 +1879,7 @@
         <v>14</v>
       </c>
       <c r="F39" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>16</v>
@@ -1896,7 +1902,7 @@
         <v>14</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C40" t="s" s="2">
         <v>14</v>
@@ -1931,7 +1937,7 @@
         <v>14</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C41" t="s" s="2">
         <v>14</v>
@@ -1966,7 +1972,7 @@
         <v>14</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C42" t="s" s="2">
         <v>14</v>
@@ -1998,10 +2004,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C43" t="s" s="2">
         <v>13</v>
@@ -2036,7 +2042,7 @@
         <v>14</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C44" t="s" s="2">
         <v>14</v>
@@ -2071,7 +2077,7 @@
         <v>14</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C45" t="s" s="2">
         <v>14</v>
@@ -2106,7 +2112,7 @@
         <v>14</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C46" t="s" s="2">
         <v>14</v>
@@ -2138,10 +2144,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C47" t="s" s="2">
         <v>13</v>
@@ -2176,7 +2182,7 @@
         <v>14</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C48" t="s" s="2">
         <v>14</v>
@@ -2208,10 +2214,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C49" t="s" s="2">
         <v>13</v>
@@ -2223,7 +2229,7 @@
         <v>14</v>
       </c>
       <c r="F49" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>16</v>
@@ -2246,7 +2252,7 @@
         <v>14</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C50" t="s" s="2">
         <v>14</v>
@@ -2281,7 +2287,7 @@
         <v>14</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C51" t="s" s="2">
         <v>14</v>
@@ -2316,7 +2322,7 @@
         <v>14</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C52" t="s" s="2">
         <v>14</v>
@@ -2348,10 +2354,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C53" t="s" s="2">
         <v>13</v>
@@ -2360,7 +2366,7 @@
         <v>14</v>
       </c>
       <c r="E53" t="s" s="2">
-        <v>67</v>
+        <v>14</v>
       </c>
       <c r="F53" t="s" s="2">
         <v>68</v>
@@ -2386,7 +2392,7 @@
         <v>14</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C54" t="s" s="2">
         <v>14</v>
@@ -2421,7 +2427,7 @@
         <v>14</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C55" t="s" s="2">
         <v>14</v>
@@ -2430,7 +2436,7 @@
         <v>14</v>
       </c>
       <c r="E55" t="s" s="2">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F55" t="s" s="2">
         <v>14</v>
@@ -2456,7 +2462,7 @@
         <v>14</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C56" t="s" s="2">
         <v>14</v>
@@ -2503,7 +2509,7 @@
         <v>71</v>
       </c>
       <c r="F57" t="s" s="2">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>16</v>
@@ -2535,7 +2541,7 @@
         <v>14</v>
       </c>
       <c r="E58" t="s" s="2">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F58" t="s" s="2">
         <v>14</v>
@@ -2570,7 +2576,7 @@
         <v>14</v>
       </c>
       <c r="E59" t="s" s="2">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F59" t="s" s="2">
         <v>14</v>
@@ -2628,19 +2634,19 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E61" t="s" s="2">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="F61" t="s" s="2">
         <v>15</v>
@@ -2663,28 +2669,28 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B62" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="B62" t="s" s="2">
-        <v>75</v>
-      </c>
       <c r="C62" t="s" s="2">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E62" t="s" s="2">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="F62" t="s" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>18</v>
@@ -2698,28 +2704,28 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D63" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E63" t="s" s="2">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="F63" t="s" s="2">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>18</v>
@@ -2736,7 +2742,7 @@
         <v>14</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C64" t="s" s="2">
         <v>14</v>
@@ -2745,7 +2751,7 @@
         <v>14</v>
       </c>
       <c r="E64" t="s" s="2">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F64" t="s" s="2">
         <v>14</v>
@@ -2768,28 +2774,28 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="B65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D65" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E65" t="s" s="2">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="F65" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>18</v>
@@ -2803,28 +2809,28 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>14</v>
+        <v>78</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D66" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E66" t="s" s="2">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F66" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>18</v>
@@ -2838,10 +2844,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C67" t="s" s="2">
         <v>13</v>
@@ -2853,7 +2859,7 @@
         <v>14</v>
       </c>
       <c r="F67" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>16</v>
@@ -2876,7 +2882,7 @@
         <v>14</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C68" t="s" s="2">
         <v>14</v>
@@ -2885,7 +2891,7 @@
         <v>14</v>
       </c>
       <c r="E68" t="s" s="2">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="F68" t="s" s="2">
         <v>14</v>
@@ -2911,7 +2917,7 @@
         <v>14</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C69" t="s" s="2">
         <v>14</v>
@@ -2920,7 +2926,7 @@
         <v>14</v>
       </c>
       <c r="E69" t="s" s="2">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="F69" t="s" s="2">
         <v>14</v>
@@ -2946,7 +2952,7 @@
         <v>14</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C70" t="s" s="2">
         <v>14</v>
@@ -2978,10 +2984,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C71" t="s" s="2">
         <v>13</v>
@@ -2993,7 +2999,7 @@
         <v>14</v>
       </c>
       <c r="F71" t="s" s="2">
-        <v>15</v>
+        <v>85</v>
       </c>
       <c r="G71" t="s" s="2">
         <v>16</v>
@@ -3016,7 +3022,7 @@
         <v>14</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C72" t="s" s="2">
         <v>14</v>
@@ -3051,7 +3057,7 @@
         <v>14</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C73" t="s" s="2">
         <v>14</v>
@@ -3086,7 +3092,7 @@
         <v>14</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C74" t="s" s="2">
         <v>14</v>
@@ -3118,10 +3124,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C75" t="s" s="2">
         <v>13</v>
@@ -3130,10 +3136,10 @@
         <v>14</v>
       </c>
       <c r="E75" t="s" s="2">
-        <v>86</v>
+        <v>14</v>
       </c>
       <c r="F75" t="s" s="2">
-        <v>87</v>
+        <v>15</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>16</v>
@@ -3156,7 +3162,7 @@
         <v>14</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C76" t="s" s="2">
         <v>14</v>
@@ -3165,7 +3171,7 @@
         <v>14</v>
       </c>
       <c r="E76" t="s" s="2">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="F76" t="s" s="2">
         <v>14</v>
@@ -3191,7 +3197,7 @@
         <v>14</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C77" t="s" s="2">
         <v>14</v>
@@ -3200,7 +3206,7 @@
         <v>14</v>
       </c>
       <c r="E77" t="s" s="2">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F77" t="s" s="2">
         <v>14</v>
@@ -3226,7 +3232,7 @@
         <v>14</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C78" t="s" s="2">
         <v>14</v>
@@ -3410,10 +3416,10 @@
         <v>14</v>
       </c>
       <c r="E83" t="s" s="2">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F83" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G83" t="s" s="2">
         <v>16</v>
@@ -3538,10 +3544,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C87" t="s" s="2">
         <v>13</v>
@@ -3550,10 +3556,10 @@
         <v>14</v>
       </c>
       <c r="E87" t="s" s="2">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="F87" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G87" t="s" s="2">
         <v>16</v>
@@ -3576,7 +3582,7 @@
         <v>14</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C88" t="s" s="2">
         <v>14</v>
@@ -3585,7 +3591,7 @@
         <v>14</v>
       </c>
       <c r="E88" t="s" s="2">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F88" t="s" s="2">
         <v>14</v>
@@ -3611,7 +3617,7 @@
         <v>14</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C89" t="s" s="2">
         <v>14</v>
@@ -3620,7 +3626,7 @@
         <v>14</v>
       </c>
       <c r="E89" t="s" s="2">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F89" t="s" s="2">
         <v>14</v>
@@ -3646,7 +3652,7 @@
         <v>14</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C90" t="s" s="2">
         <v>14</v>
@@ -3678,10 +3684,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C91" t="s" s="2">
         <v>13</v>
@@ -3690,10 +3696,10 @@
         <v>14</v>
       </c>
       <c r="E91" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F91" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G91" t="s" s="2">
         <v>16</v>
@@ -3716,7 +3722,7 @@
         <v>14</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C92" t="s" s="2">
         <v>14</v>
@@ -3751,7 +3757,7 @@
         <v>14</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C93" t="s" s="2">
         <v>14</v>
@@ -3786,7 +3792,7 @@
         <v>14</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C94" t="s" s="2">
         <v>14</v>
@@ -3818,10 +3824,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C95" t="s" s="2">
         <v>13</v>
@@ -3830,10 +3836,10 @@
         <v>14</v>
       </c>
       <c r="E95" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F95" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G95" t="s" s="2">
         <v>16</v>
@@ -3856,7 +3862,7 @@
         <v>14</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C96" t="s" s="2">
         <v>14</v>
@@ -3891,7 +3897,7 @@
         <v>14</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C97" t="s" s="2">
         <v>14</v>
@@ -3926,7 +3932,7 @@
         <v>14</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C98" t="s" s="2">
         <v>14</v>
@@ -3958,10 +3964,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C99" t="s" s="2">
         <v>13</v>
@@ -3970,7 +3976,7 @@
         <v>14</v>
       </c>
       <c r="E99" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F99" t="s" s="2">
         <v>15</v>
@@ -3996,7 +4002,7 @@
         <v>14</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C100" t="s" s="2">
         <v>14</v>
@@ -4031,7 +4037,7 @@
         <v>14</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C101" t="s" s="2">
         <v>14</v>
@@ -4066,7 +4072,7 @@
         <v>14</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C102" t="s" s="2">
         <v>14</v>
@@ -4098,10 +4104,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C103" t="s" s="2">
         <v>13</v>
@@ -4110,10 +4116,10 @@
         <v>14</v>
       </c>
       <c r="E103" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F103" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G103" t="s" s="2">
         <v>16</v>
@@ -4136,7 +4142,7 @@
         <v>14</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C104" t="s" s="2">
         <v>14</v>
@@ -4171,7 +4177,7 @@
         <v>14</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C105" t="s" s="2">
         <v>14</v>
@@ -4206,7 +4212,7 @@
         <v>14</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C106" t="s" s="2">
         <v>14</v>
@@ -4238,10 +4244,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C107" t="s" s="2">
         <v>13</v>
@@ -4276,7 +4282,7 @@
         <v>14</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C108" t="s" s="2">
         <v>14</v>
@@ -4311,7 +4317,7 @@
         <v>14</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C109" t="s" s="2">
         <v>14</v>
@@ -4346,7 +4352,7 @@
         <v>14</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C110" t="s" s="2">
         <v>14</v>
@@ -4378,10 +4384,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C111" t="s" s="2">
         <v>13</v>
@@ -4390,7 +4396,7 @@
         <v>14</v>
       </c>
       <c r="E111" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F111" t="s" s="2">
         <v>15</v>
@@ -4416,7 +4422,7 @@
         <v>14</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C112" t="s" s="2">
         <v>14</v>
@@ -4451,7 +4457,7 @@
         <v>14</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C113" t="s" s="2">
         <v>14</v>
@@ -4486,7 +4492,7 @@
         <v>14</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C114" t="s" s="2">
         <v>14</v>
@@ -4518,10 +4524,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C115" t="s" s="2">
         <v>13</v>
@@ -4533,7 +4539,7 @@
         <v>14</v>
       </c>
       <c r="F115" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G115" t="s" s="2">
         <v>16</v>
@@ -4556,7 +4562,7 @@
         <v>14</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C116" t="s" s="2">
         <v>14</v>
@@ -4591,7 +4597,7 @@
         <v>14</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C117" t="s" s="2">
         <v>14</v>
@@ -4626,7 +4632,7 @@
         <v>14</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C118" t="s" s="2">
         <v>14</v>
@@ -4658,10 +4664,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>31</v>
+        <v>123</v>
       </c>
       <c r="C119" t="s" s="2">
         <v>13</v>
@@ -4696,7 +4702,7 @@
         <v>14</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>31</v>
+        <v>123</v>
       </c>
       <c r="C120" t="s" s="2">
         <v>14</v>
@@ -4731,7 +4737,7 @@
         <v>14</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>31</v>
+        <v>123</v>
       </c>
       <c r="C121" t="s" s="2">
         <v>14</v>
@@ -4766,7 +4772,7 @@
         <v>14</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>31</v>
+        <v>123</v>
       </c>
       <c r="C122" t="s" s="2">
         <v>14</v>
@@ -4798,10 +4804,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C123" t="s" s="2">
         <v>13</v>
@@ -4836,7 +4842,7 @@
         <v>14</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C124" t="s" s="2">
         <v>14</v>
@@ -4871,7 +4877,7 @@
         <v>14</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C125" t="s" s="2">
         <v>14</v>
@@ -4906,7 +4912,7 @@
         <v>14</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C126" t="s" s="2">
         <v>14</v>
@@ -4938,10 +4944,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C127" t="s" s="2">
         <v>13</v>
@@ -4976,7 +4982,7 @@
         <v>14</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C128" t="s" s="2">
         <v>14</v>
@@ -5011,7 +5017,7 @@
         <v>14</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C129" t="s" s="2">
         <v>14</v>
@@ -5046,7 +5052,7 @@
         <v>14</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C130" t="s" s="2">
         <v>14</v>

--- a/branches/release/v2027.0.0-ballot.rc2/observations-summary.xlsx
+++ b/branches/release/v2027.0.0-ballot.rc2/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1430" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1430" uniqueCount="135">
   <si>
     <t>Profile</t>
   </si>
@@ -59,51 +59,57 @@
     <t/>
   </si>
   <si>
+    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-lungenfunktion/ValueSet/mii-vs-lufu-lnc-observable (preferred)</t>
+  </si>
+  <si>
+    <t>dateTime, Period, Timing, instant</t>
+  </si>
+  <si>
+    <t>Quantityĵ</t>
+  </si>
+  <si>
+    <t>optional</t>
+  </si>
+  <si>
+    <t>Quantity, CodeableConcept, string, boolean, integer, Range, Ratio, SampledData, time, dateTime, Period</t>
+  </si>
+  <si>
+    <t>SNOMED CT#1078210003</t>
+  </si>
+  <si>
+    <t>mii-pr-lungenfunktion-bf</t>
+  </si>
+  <si>
+    <t>MII PR Lungenfunktion BF</t>
+  </si>
+  <si>
+    <t>Observation Category Codes#vital-signs</t>
+  </si>
+  <si>
+    <t>null#9279-1, null#271625008</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes (example)</t>
+  </si>
+  <si>
+    <t>dateTime, Period</t>
+  </si>
+  <si>
+    <t>mii-pr-lungenfunktion-co2-konzentration</t>
+  </si>
+  <si>
+    <t>MII PR Lungenfunktion CO2 Konzentration</t>
+  </si>
+  <si>
+    <t>Observation Category Codes#social-history</t>
+  </si>
+  <si>
+    <t>null#250780004</t>
+  </si>
+  <si>
     <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1 (example)</t>
   </si>
   <si>
-    <t>dateTime, Period, Timing, instant</t>
-  </si>
-  <si>
-    <t>Quantityĵ</t>
-  </si>
-  <si>
-    <t>optional</t>
-  </si>
-  <si>
-    <t>Quantity, CodeableConcept, string, boolean, integer, Range, Ratio, SampledData, time, dateTime, Period</t>
-  </si>
-  <si>
-    <t>SNOMED CT#1078210003</t>
-  </si>
-  <si>
-    <t>mii-pr-lungenfunktion-bf</t>
-  </si>
-  <si>
-    <t>MII PR Lungenfunktion BF</t>
-  </si>
-  <si>
-    <t>Observation Category Codes#vital-signs</t>
-  </si>
-  <si>
-    <t>null#9279-1, null#271625008</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes (example)</t>
-  </si>
-  <si>
-    <t>dateTime, Period</t>
-  </si>
-  <si>
-    <t>mii-pr-lungenfunktion-co2-konzentration</t>
-  </si>
-  <si>
-    <t>MII PR Lungenfunktion CO2 Konzentration</t>
-  </si>
-  <si>
-    <t>Observation Category Codes#social-history</t>
-  </si>
-  <si>
     <t>mii-pr-lungenfunktion-diffusionskapazitaet</t>
   </si>
   <si>
@@ -146,6 +152,9 @@
     <t>MII PR Lungenfunktion Dosis</t>
   </si>
   <si>
+    <t>null#1376040001, null#65866-6</t>
+  </si>
+  <si>
     <t>mii-pr-lungenfunktion-fev</t>
   </si>
   <si>
@@ -203,12 +212,18 @@
     <t>MII PR Lungenfunktion Hb</t>
   </si>
   <si>
+    <t>null#38082009, null#718-7</t>
+  </si>
+  <si>
     <t>mii-pr-lungenfunktion-ic</t>
   </si>
   <si>
     <t>MII PR Lungenfunktion IC</t>
   </si>
   <si>
+    <t>null#29533001</t>
+  </si>
+  <si>
     <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-lungenfunktion/ValueSet/mii-vs-lufu-lnc-ic (required)</t>
   </si>
   <si>
@@ -239,7 +254,7 @@
     <t>MII PR Lungenfunktion KCOc</t>
   </si>
   <si>
-    <t>null#69578-3</t>
+    <t>null#TODO, null#69578-3</t>
   </si>
   <si>
     <t>mii-pr-lungenfunktion-luftfeuchtigkeit</t>
@@ -248,10 +263,16 @@
     <t>MII PR Lungenfunktion Luftfeuchtigkeit</t>
   </si>
   <si>
+    <t>null#3525006</t>
+  </si>
+  <si>
     <t>mii-pr-lungenfunktion-lufttemperatur</t>
   </si>
   <si>
     <t>MII PR Lungenfunktion Lufttemperatur</t>
+  </si>
+  <si>
+    <t>null#250825003</t>
   </si>
   <si>
     <t>mii-pr-lungenfunktion-mef</t>
@@ -826,10 +847,10 @@
         <v>14</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F9" t="s" s="2">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>16</v>
@@ -849,10 +870,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s" s="2">
         <v>13</v>
@@ -887,7 +908,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s" s="2">
         <v>14</v>
@@ -922,7 +943,7 @@
         <v>14</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s" s="2">
         <v>14</v>
@@ -957,7 +978,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s" s="2">
         <v>14</v>
@@ -989,10 +1010,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C14" t="s" s="2">
         <v>13</v>
@@ -1001,10 +1022,10 @@
         <v>14</v>
       </c>
       <c r="E14" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F14" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>16</v>
@@ -1027,7 +1048,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s" s="2">
         <v>14</v>
@@ -1036,7 +1057,7 @@
         <v>14</v>
       </c>
       <c r="E15" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F15" t="s" s="2">
         <v>14</v>
@@ -1062,7 +1083,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s" s="2">
         <v>14</v>
@@ -1071,7 +1092,7 @@
         <v>14</v>
       </c>
       <c r="E16" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F16" t="s" s="2">
         <v>14</v>
@@ -1097,7 +1118,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s" s="2">
         <v>14</v>
@@ -1129,10 +1150,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C18" t="s" s="2">
         <v>13</v>
@@ -1141,10 +1162,10 @@
         <v>14</v>
       </c>
       <c r="E18" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F18" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>16</v>
@@ -1167,7 +1188,7 @@
         <v>14</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C19" t="s" s="2">
         <v>14</v>
@@ -1176,7 +1197,7 @@
         <v>14</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F19" t="s" s="2">
         <v>14</v>
@@ -1202,7 +1223,7 @@
         <v>14</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C20" t="s" s="2">
         <v>14</v>
@@ -1211,7 +1232,7 @@
         <v>14</v>
       </c>
       <c r="E20" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F20" t="s" s="2">
         <v>14</v>
@@ -1237,7 +1258,7 @@
         <v>14</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C21" t="s" s="2">
         <v>14</v>
@@ -1269,10 +1290,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C22" t="s" s="2">
         <v>13</v>
@@ -1281,10 +1302,10 @@
         <v>14</v>
       </c>
       <c r="E22" t="s" s="2">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="F22" t="s" s="2">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>16</v>
@@ -1304,10 +1325,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C23" t="s" s="2">
         <v>13</v>
@@ -1319,7 +1340,7 @@
         <v>14</v>
       </c>
       <c r="F23" t="s" s="2">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>16</v>
@@ -1342,7 +1363,7 @@
         <v>14</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C24" t="s" s="2">
         <v>14</v>
@@ -1377,7 +1398,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C25" t="s" s="2">
         <v>14</v>
@@ -1412,7 +1433,7 @@
         <v>14</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C26" t="s" s="2">
         <v>14</v>
@@ -1444,10 +1465,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C27" t="s" s="2">
         <v>13</v>
@@ -1459,7 +1480,7 @@
         <v>14</v>
       </c>
       <c r="F27" t="s" s="2">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>16</v>
@@ -1482,7 +1503,7 @@
         <v>14</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C28" t="s" s="2">
         <v>14</v>
@@ -1517,7 +1538,7 @@
         <v>14</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C29" t="s" s="2">
         <v>14</v>
@@ -1552,7 +1573,7 @@
         <v>14</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C30" t="s" s="2">
         <v>14</v>
@@ -1584,10 +1605,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C31" t="s" s="2">
         <v>13</v>
@@ -1622,7 +1643,7 @@
         <v>14</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C32" t="s" s="2">
         <v>14</v>
@@ -1657,7 +1678,7 @@
         <v>14</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C33" t="s" s="2">
         <v>14</v>
@@ -1692,7 +1713,7 @@
         <v>14</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C34" t="s" s="2">
         <v>14</v>
@@ -1724,10 +1745,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C35" t="s" s="2">
         <v>13</v>
@@ -1736,10 +1757,10 @@
         <v>14</v>
       </c>
       <c r="E35" t="s" s="2">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F35" t="s" s="2">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>16</v>
@@ -1762,7 +1783,7 @@
         <v>14</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C36" t="s" s="2">
         <v>14</v>
@@ -1771,7 +1792,7 @@
         <v>14</v>
       </c>
       <c r="E36" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F36" t="s" s="2">
         <v>14</v>
@@ -1797,7 +1818,7 @@
         <v>14</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C37" t="s" s="2">
         <v>14</v>
@@ -1806,7 +1827,7 @@
         <v>14</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>14</v>
@@ -1832,7 +1853,7 @@
         <v>14</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C38" t="s" s="2">
         <v>14</v>
@@ -1864,10 +1885,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C39" t="s" s="2">
         <v>13</v>
@@ -1879,7 +1900,7 @@
         <v>14</v>
       </c>
       <c r="F39" t="s" s="2">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>16</v>
@@ -1902,7 +1923,7 @@
         <v>14</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C40" t="s" s="2">
         <v>14</v>
@@ -1937,7 +1958,7 @@
         <v>14</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C41" t="s" s="2">
         <v>14</v>
@@ -1972,7 +1993,7 @@
         <v>14</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C42" t="s" s="2">
         <v>14</v>
@@ -2004,10 +2025,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C43" t="s" s="2">
         <v>13</v>
@@ -2042,7 +2063,7 @@
         <v>14</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C44" t="s" s="2">
         <v>14</v>
@@ -2077,7 +2098,7 @@
         <v>14</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C45" t="s" s="2">
         <v>14</v>
@@ -2112,7 +2133,7 @@
         <v>14</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C46" t="s" s="2">
         <v>14</v>
@@ -2144,10 +2165,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C47" t="s" s="2">
         <v>13</v>
@@ -2156,10 +2177,10 @@
         <v>14</v>
       </c>
       <c r="E47" t="s" s="2">
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="F47" t="s" s="2">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>16</v>
@@ -2182,7 +2203,7 @@
         <v>14</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C48" t="s" s="2">
         <v>14</v>
@@ -2214,10 +2235,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C49" t="s" s="2">
         <v>13</v>
@@ -2226,10 +2247,10 @@
         <v>14</v>
       </c>
       <c r="E49" t="s" s="2">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="F49" t="s" s="2">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>16</v>
@@ -2252,7 +2273,7 @@
         <v>14</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C50" t="s" s="2">
         <v>14</v>
@@ -2261,7 +2282,7 @@
         <v>14</v>
       </c>
       <c r="E50" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F50" t="s" s="2">
         <v>14</v>
@@ -2287,7 +2308,7 @@
         <v>14</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C51" t="s" s="2">
         <v>14</v>
@@ -2296,7 +2317,7 @@
         <v>14</v>
       </c>
       <c r="E51" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F51" t="s" s="2">
         <v>14</v>
@@ -2322,7 +2343,7 @@
         <v>14</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C52" t="s" s="2">
         <v>14</v>
@@ -2354,10 +2375,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C53" t="s" s="2">
         <v>13</v>
@@ -2369,7 +2390,7 @@
         <v>14</v>
       </c>
       <c r="F53" t="s" s="2">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>16</v>
@@ -2392,7 +2413,7 @@
         <v>14</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C54" t="s" s="2">
         <v>14</v>
@@ -2401,7 +2422,7 @@
         <v>14</v>
       </c>
       <c r="E54" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F54" t="s" s="2">
         <v>14</v>
@@ -2427,7 +2448,7 @@
         <v>14</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C55" t="s" s="2">
         <v>14</v>
@@ -2436,7 +2457,7 @@
         <v>14</v>
       </c>
       <c r="E55" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F55" t="s" s="2">
         <v>14</v>
@@ -2462,7 +2483,7 @@
         <v>14</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C56" t="s" s="2">
         <v>14</v>
@@ -2494,10 +2515,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C57" t="s" s="2">
         <v>13</v>
@@ -2506,10 +2527,10 @@
         <v>14</v>
       </c>
       <c r="E57" t="s" s="2">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F57" t="s" s="2">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>16</v>
@@ -2532,7 +2553,7 @@
         <v>14</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C58" t="s" s="2">
         <v>14</v>
@@ -2541,7 +2562,7 @@
         <v>14</v>
       </c>
       <c r="E58" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F58" t="s" s="2">
         <v>14</v>
@@ -2567,7 +2588,7 @@
         <v>14</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C59" t="s" s="2">
         <v>14</v>
@@ -2576,7 +2597,7 @@
         <v>14</v>
       </c>
       <c r="E59" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F59" t="s" s="2">
         <v>14</v>
@@ -2602,7 +2623,7 @@
         <v>14</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C60" t="s" s="2">
         <v>14</v>
@@ -2634,10 +2655,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C61" t="s" s="2">
         <v>13</v>
@@ -2646,10 +2667,10 @@
         <v>14</v>
       </c>
       <c r="E61" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F61" t="s" s="2">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>16</v>
@@ -2672,7 +2693,7 @@
         <v>14</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C62" t="s" s="2">
         <v>14</v>
@@ -2681,7 +2702,7 @@
         <v>14</v>
       </c>
       <c r="E62" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F62" t="s" s="2">
         <v>14</v>
@@ -2707,7 +2728,7 @@
         <v>14</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C63" t="s" s="2">
         <v>14</v>
@@ -2716,7 +2737,7 @@
         <v>14</v>
       </c>
       <c r="E63" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F63" t="s" s="2">
         <v>14</v>
@@ -2742,7 +2763,7 @@
         <v>14</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C64" t="s" s="2">
         <v>14</v>
@@ -2774,10 +2795,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C65" t="s" s="2">
         <v>29</v>
@@ -2786,10 +2807,10 @@
         <v>14</v>
       </c>
       <c r="E65" t="s" s="2">
-        <v>14</v>
+        <v>83</v>
       </c>
       <c r="F65" t="s" s="2">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G65" t="s" s="2">
         <v>16</v>
@@ -2809,10 +2830,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C66" t="s" s="2">
         <v>29</v>
@@ -2821,10 +2842,10 @@
         <v>14</v>
       </c>
       <c r="E66" t="s" s="2">
-        <v>14</v>
+        <v>86</v>
       </c>
       <c r="F66" t="s" s="2">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>16</v>
@@ -2844,10 +2865,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="C67" t="s" s="2">
         <v>13</v>
@@ -2859,7 +2880,7 @@
         <v>14</v>
       </c>
       <c r="F67" t="s" s="2">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>16</v>
@@ -2882,7 +2903,7 @@
         <v>14</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="C68" t="s" s="2">
         <v>14</v>
@@ -2891,7 +2912,7 @@
         <v>14</v>
       </c>
       <c r="E68" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F68" t="s" s="2">
         <v>14</v>
@@ -2917,7 +2938,7 @@
         <v>14</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="C69" t="s" s="2">
         <v>14</v>
@@ -2926,7 +2947,7 @@
         <v>14</v>
       </c>
       <c r="E69" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F69" t="s" s="2">
         <v>14</v>
@@ -2952,7 +2973,7 @@
         <v>14</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="C70" t="s" s="2">
         <v>14</v>
@@ -2984,10 +3005,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C71" t="s" s="2">
         <v>13</v>
@@ -2999,7 +3020,7 @@
         <v>14</v>
       </c>
       <c r="F71" t="s" s="2">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G71" t="s" s="2">
         <v>16</v>
@@ -3022,7 +3043,7 @@
         <v>14</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C72" t="s" s="2">
         <v>14</v>
@@ -3057,7 +3078,7 @@
         <v>14</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C73" t="s" s="2">
         <v>14</v>
@@ -3092,7 +3113,7 @@
         <v>14</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C74" t="s" s="2">
         <v>14</v>
@@ -3124,10 +3145,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C75" t="s" s="2">
         <v>13</v>
@@ -3162,7 +3183,7 @@
         <v>14</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C76" t="s" s="2">
         <v>14</v>
@@ -3197,7 +3218,7 @@
         <v>14</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C77" t="s" s="2">
         <v>14</v>
@@ -3232,7 +3253,7 @@
         <v>14</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C78" t="s" s="2">
         <v>14</v>
@@ -3264,10 +3285,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="C79" t="s" s="2">
         <v>13</v>
@@ -3276,10 +3297,10 @@
         <v>14</v>
       </c>
       <c r="E79" t="s" s="2">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="F79" t="s" s="2">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="G79" t="s" s="2">
         <v>16</v>
@@ -3302,7 +3323,7 @@
         <v>14</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="C80" t="s" s="2">
         <v>14</v>
@@ -3311,7 +3332,7 @@
         <v>14</v>
       </c>
       <c r="E80" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F80" t="s" s="2">
         <v>14</v>
@@ -3337,7 +3358,7 @@
         <v>14</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="C81" t="s" s="2">
         <v>14</v>
@@ -3346,7 +3367,7 @@
         <v>14</v>
       </c>
       <c r="E81" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F81" t="s" s="2">
         <v>14</v>
@@ -3372,7 +3393,7 @@
         <v>14</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="C82" t="s" s="2">
         <v>14</v>
@@ -3404,10 +3425,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="C83" t="s" s="2">
         <v>13</v>
@@ -3416,10 +3437,10 @@
         <v>14</v>
       </c>
       <c r="E83" t="s" s="2">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="F83" t="s" s="2">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="G83" t="s" s="2">
         <v>16</v>
@@ -3442,7 +3463,7 @@
         <v>14</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="C84" t="s" s="2">
         <v>14</v>
@@ -3451,7 +3472,7 @@
         <v>14</v>
       </c>
       <c r="E84" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F84" t="s" s="2">
         <v>14</v>
@@ -3477,7 +3498,7 @@
         <v>14</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="C85" t="s" s="2">
         <v>14</v>
@@ -3486,7 +3507,7 @@
         <v>14</v>
       </c>
       <c r="E85" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F85" t="s" s="2">
         <v>14</v>
@@ -3512,7 +3533,7 @@
         <v>14</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="C86" t="s" s="2">
         <v>14</v>
@@ -3544,10 +3565,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C87" t="s" s="2">
         <v>13</v>
@@ -3556,10 +3577,10 @@
         <v>14</v>
       </c>
       <c r="E87" t="s" s="2">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="F87" t="s" s="2">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="G87" t="s" s="2">
         <v>16</v>
@@ -3582,7 +3603,7 @@
         <v>14</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C88" t="s" s="2">
         <v>14</v>
@@ -3591,7 +3612,7 @@
         <v>14</v>
       </c>
       <c r="E88" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F88" t="s" s="2">
         <v>14</v>
@@ -3617,7 +3638,7 @@
         <v>14</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C89" t="s" s="2">
         <v>14</v>
@@ -3626,7 +3647,7 @@
         <v>14</v>
       </c>
       <c r="E89" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F89" t="s" s="2">
         <v>14</v>
@@ -3652,7 +3673,7 @@
         <v>14</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C90" t="s" s="2">
         <v>14</v>
@@ -3684,10 +3705,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="C91" t="s" s="2">
         <v>13</v>
@@ -3696,10 +3717,10 @@
         <v>14</v>
       </c>
       <c r="E91" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="F91" t="s" s="2">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="G91" t="s" s="2">
         <v>16</v>
@@ -3722,7 +3743,7 @@
         <v>14</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="C92" t="s" s="2">
         <v>14</v>
@@ -3731,7 +3752,7 @@
         <v>14</v>
       </c>
       <c r="E92" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F92" t="s" s="2">
         <v>14</v>
@@ -3757,7 +3778,7 @@
         <v>14</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="C93" t="s" s="2">
         <v>14</v>
@@ -3766,7 +3787,7 @@
         <v>14</v>
       </c>
       <c r="E93" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F93" t="s" s="2">
         <v>14</v>
@@ -3792,7 +3813,7 @@
         <v>14</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="C94" t="s" s="2">
         <v>14</v>
@@ -3824,10 +3845,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="C95" t="s" s="2">
         <v>13</v>
@@ -3836,10 +3857,10 @@
         <v>14</v>
       </c>
       <c r="E95" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="F95" t="s" s="2">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="G95" t="s" s="2">
         <v>16</v>
@@ -3862,7 +3883,7 @@
         <v>14</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="C96" t="s" s="2">
         <v>14</v>
@@ -3871,7 +3892,7 @@
         <v>14</v>
       </c>
       <c r="E96" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F96" t="s" s="2">
         <v>14</v>
@@ -3897,7 +3918,7 @@
         <v>14</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="C97" t="s" s="2">
         <v>14</v>
@@ -3906,7 +3927,7 @@
         <v>14</v>
       </c>
       <c r="E97" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F97" t="s" s="2">
         <v>14</v>
@@ -3932,7 +3953,7 @@
         <v>14</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="C98" t="s" s="2">
         <v>14</v>
@@ -3964,10 +3985,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="C99" t="s" s="2">
         <v>13</v>
@@ -3976,10 +3997,10 @@
         <v>14</v>
       </c>
       <c r="E99" t="s" s="2">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="F99" t="s" s="2">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G99" t="s" s="2">
         <v>16</v>
@@ -4002,7 +4023,7 @@
         <v>14</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="C100" t="s" s="2">
         <v>14</v>
@@ -4011,7 +4032,7 @@
         <v>14</v>
       </c>
       <c r="E100" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F100" t="s" s="2">
         <v>14</v>
@@ -4037,7 +4058,7 @@
         <v>14</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="C101" t="s" s="2">
         <v>14</v>
@@ -4046,7 +4067,7 @@
         <v>14</v>
       </c>
       <c r="E101" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F101" t="s" s="2">
         <v>14</v>
@@ -4072,7 +4093,7 @@
         <v>14</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="C102" t="s" s="2">
         <v>14</v>
@@ -4104,10 +4125,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C103" t="s" s="2">
         <v>13</v>
@@ -4116,10 +4137,10 @@
         <v>14</v>
       </c>
       <c r="E103" t="s" s="2">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="F103" t="s" s="2">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="G103" t="s" s="2">
         <v>16</v>
@@ -4142,7 +4163,7 @@
         <v>14</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C104" t="s" s="2">
         <v>14</v>
@@ -4151,7 +4172,7 @@
         <v>14</v>
       </c>
       <c r="E104" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F104" t="s" s="2">
         <v>14</v>
@@ -4177,7 +4198,7 @@
         <v>14</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C105" t="s" s="2">
         <v>14</v>
@@ -4186,7 +4207,7 @@
         <v>14</v>
       </c>
       <c r="E105" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F105" t="s" s="2">
         <v>14</v>
@@ -4212,7 +4233,7 @@
         <v>14</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C106" t="s" s="2">
         <v>14</v>
@@ -4244,10 +4265,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="C107" t="s" s="2">
         <v>13</v>
@@ -4282,7 +4303,7 @@
         <v>14</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="C108" t="s" s="2">
         <v>14</v>
@@ -4317,7 +4338,7 @@
         <v>14</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="C109" t="s" s="2">
         <v>14</v>
@@ -4352,7 +4373,7 @@
         <v>14</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="C110" t="s" s="2">
         <v>14</v>
@@ -4384,10 +4405,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="C111" t="s" s="2">
         <v>13</v>
@@ -4396,10 +4417,10 @@
         <v>14</v>
       </c>
       <c r="E111" t="s" s="2">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="F111" t="s" s="2">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G111" t="s" s="2">
         <v>16</v>
@@ -4422,7 +4443,7 @@
         <v>14</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="C112" t="s" s="2">
         <v>14</v>
@@ -4431,7 +4452,7 @@
         <v>14</v>
       </c>
       <c r="E112" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F112" t="s" s="2">
         <v>14</v>
@@ -4457,7 +4478,7 @@
         <v>14</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="C113" t="s" s="2">
         <v>14</v>
@@ -4466,7 +4487,7 @@
         <v>14</v>
       </c>
       <c r="E113" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F113" t="s" s="2">
         <v>14</v>
@@ -4492,7 +4513,7 @@
         <v>14</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="C114" t="s" s="2">
         <v>14</v>
@@ -4524,10 +4545,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="C115" t="s" s="2">
         <v>13</v>
@@ -4539,7 +4560,7 @@
         <v>14</v>
       </c>
       <c r="F115" t="s" s="2">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="G115" t="s" s="2">
         <v>16</v>
@@ -4562,7 +4583,7 @@
         <v>14</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="C116" t="s" s="2">
         <v>14</v>
@@ -4571,7 +4592,7 @@
         <v>14</v>
       </c>
       <c r="E116" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F116" t="s" s="2">
         <v>14</v>
@@ -4597,7 +4618,7 @@
         <v>14</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="C117" t="s" s="2">
         <v>14</v>
@@ -4632,7 +4653,7 @@
         <v>14</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="C118" t="s" s="2">
         <v>14</v>
@@ -4664,10 +4685,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="C119" t="s" s="2">
         <v>13</v>
@@ -4702,7 +4723,7 @@
         <v>14</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="C120" t="s" s="2">
         <v>14</v>
@@ -4737,7 +4758,7 @@
         <v>14</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="C121" t="s" s="2">
         <v>14</v>
@@ -4772,7 +4793,7 @@
         <v>14</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="C122" t="s" s="2">
         <v>14</v>
@@ -4804,10 +4825,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="C123" t="s" s="2">
         <v>13</v>
@@ -4842,7 +4863,7 @@
         <v>14</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="C124" t="s" s="2">
         <v>14</v>
@@ -4877,7 +4898,7 @@
         <v>14</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="C125" t="s" s="2">
         <v>14</v>
@@ -4912,7 +4933,7 @@
         <v>14</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="C126" t="s" s="2">
         <v>14</v>
@@ -4944,10 +4965,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C127" t="s" s="2">
         <v>13</v>
@@ -4982,7 +5003,7 @@
         <v>14</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C128" t="s" s="2">
         <v>14</v>
@@ -5017,7 +5038,7 @@
         <v>14</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C129" t="s" s="2">
         <v>14</v>
@@ -5052,7 +5073,7 @@
         <v>14</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C130" t="s" s="2">
         <v>14</v>
